--- a/Docs/TablasDatos-Lab6.xlsx
+++ b/Docs/TablasDatos-Lab6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universidad\2025-2\Asistencia\Laboratorios\Lab6\ISIS1225-Laboratorio-6\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\UNIANDES\EDA\LAB06\Laboratorio06-G07\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD33DA02-4501-4B58-9D83-E0FFBD1B4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95396EE-110D-4AF4-9443-547BCC4BC453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Lab6" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Carga de Catálogo PROBING (-large)</t>
   </si>
@@ -71,6 +71,54 @@
   </si>
   <si>
     <t>Tiempo de Ejecución Real @SC [ms]</t>
+  </si>
+  <si>
+    <t>46864.65</t>
+  </si>
+  <si>
+    <t>1611279.97</t>
+  </si>
+  <si>
+    <t>48204.05</t>
+  </si>
+  <si>
+    <t>1962774.39</t>
+  </si>
+  <si>
+    <t>52952.84</t>
+  </si>
+  <si>
+    <t>2600457.70</t>
+  </si>
+  <si>
+    <t>239854.04</t>
+  </si>
+  <si>
+    <t>11611130.90</t>
+  </si>
+  <si>
+    <t>34370.24</t>
+  </si>
+  <si>
+    <t>528213.02</t>
+  </si>
+  <si>
+    <t>573268.12</t>
+  </si>
+  <si>
+    <t>32869.12</t>
+  </si>
+  <si>
+    <t>668048.81</t>
+  </si>
+  <si>
+    <t>33265.89</t>
+  </si>
+  <si>
+    <t>951270.25</t>
+  </si>
+  <si>
+    <t>39366.30</t>
   </si>
 </sst>
 </file>
@@ -621,13 +669,24 @@
             </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
-            <c:numRef>
+            <c:strRef>
               <c:f>'Datos Lab6'!$B$3:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+              <c:strCache>
                 <c:ptCount val="4"/>
-              </c:numCache>
-            </c:numRef>
+                <c:pt idx="0">
+                  <c:v>11611130.90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2600457.70</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1962774.39</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1611279.97</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
@@ -635,6 +694,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -728,13 +799,24 @@
             </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
-            <c:numRef>
+            <c:strRef>
               <c:f>'Datos Lab6'!$B$11:$B$14</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+              <c:strCache>
                 <c:ptCount val="4"/>
-              </c:numCache>
-            </c:numRef>
+                <c:pt idx="0">
+                  <c:v>951270.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>668048.81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>573268.12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>528213.02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
@@ -742,6 +824,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1299,6 +1393,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1445,6 +1551,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2839,7 +2957,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="8672015" cy="6293134"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -2872,7 +2990,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="8672015" cy="6293134"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -3223,21 +3341,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B14742-4EBB-4241-AC8A-0E5F24F7BB7B}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3248,42 +3366,58 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>0.1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="7"/>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>0.5</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="7"/>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>0.7</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10">
         <v>0.9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="7"/>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
     </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -3294,35 +3428,51 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>2</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>6</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>8</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="23" ht="14.65" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.65" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -3337,14 +3487,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="164883f8-7691-4ecf-b54a-664c0d0edefe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3597,21 +3745,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="85e30bcc-d76c-4413-8e4d-2dce22fb0743" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="164883f8-7691-4ecf-b54a-664c0d0edefe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
-    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3636,9 +3783,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="85e30bcc-d76c-4413-8e4d-2dce22fb0743"/>
+    <ds:schemaRef ds:uri="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>